--- a/test/session--empty-statements/reference/2 semester 15 subjects/рік/25-1/Відомості 25-1.xlsx
+++ b/test/session--empty-statements/reference/2 semester 15 subjects/рік/25-1/Відомості 25-1.xlsx
@@ -35,7 +35,7 @@
     <definedName name="Ф80" localSheetId="5">#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Зведена J3'!$C$3:$T$20</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcMode="autoNoTable" fullCalcOnLoad="1"/>
+  <calcPr calcId="152511" calcMode="autoNoTable" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="F55" s="63">
-        <f>IF(F52="Очікую","Очікую",IF(F52-COUNTIF($U$10:$U46," - ")&lt;ROUNDDOWN(F52*0.4,0),F52-COUNTIF($U$10:$U46," - "),ROUNDDOWN(F52*0.4,0)))</f>
+        <f>IF(F52="Очікую","Очікую",IF(F52-COUNTIF($U$10:$U46," - ")&lt;ROUNDDOWN(F52*0.45,0),F52-COUNTIF($U$10:$U46," - "),ROUNDDOWN(F52*0.45,0)))</f>
         <v/>
       </c>
       <c r="G55" s="6" t="n"/>
@@ -3281,7 +3281,7 @@
       <c r="O55" s="6" t="n"/>
       <c r="P55" s="54" t="inlineStr">
         <is>
-          <t>Margarita BRITIKOVA</t>
+          <t>Маргарита БРІТІКОВА</t>
         </is>
       </c>
       <c r="Q55" s="54" t="n"/>
@@ -3569,7 +3569,7 @@
       <c r="B5" s="12" t="n"/>
       <c r="C5" s="73" t="inlineStr">
         <is>
-          <t>Успішності студентів спеціальності D5 ««Маркетинг»»</t>
+          <t>Успішності студентів спеціальності D5 «Маркетинг»</t>
         </is>
       </c>
       <c r="D5" s="92" t="n"/>
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="F38" s="63">
-        <f>IF(F35="Очікую","Очікую",IF(F35-COUNTIF($U$10:$U29," - ")&lt;ROUNDDOWN(F35*0.4,0),F35-COUNTIF($U$10:$U29," - "),ROUNDDOWN(F35*0.4,0)))</f>
+        <f>IF(F35="Очікую","Очікую",IF(F35-COUNTIF($U$10:$U29," - ")&lt;ROUNDDOWN(F35*0.45,0),F35-COUNTIF($U$10:$U29," - "),ROUNDDOWN(F35*0.45,0)))</f>
         <v/>
       </c>
       <c r="G38" s="6" t="n"/>
@@ -5805,7 +5805,7 @@
       <c r="O38" s="6" t="n"/>
       <c r="P38" s="56" t="inlineStr">
         <is>
-          <t>Margarita BRITIKOVA</t>
+          <t>Маргарита БРІТІКОВА</t>
         </is>
       </c>
       <c r="Q38" s="54" t="n"/>
@@ -6114,7 +6114,7 @@
       <c r="B5" s="12" t="n"/>
       <c r="C5" s="73" t="inlineStr">
         <is>
-          <t>Успішності студентів спеціальності E2 ««Екологія»»</t>
+          <t>Успішності студентів спеціальності E2 «Екологія»</t>
         </is>
       </c>
       <c r="D5" s="92" t="n"/>
@@ -7765,7 +7765,7 @@
         </is>
       </c>
       <c r="F31" s="63">
-        <f>IF(F28="Очікую","Очікую",IF(F28-COUNTIF($U$10:$U22," - ")&lt;ROUNDDOWN(F28*0.4,0),F28-COUNTIF($U$10:$U22," - "),ROUNDDOWN(F28*0.4,0)))</f>
+        <f>IF(F28="Очікую","Очікую",IF(F28-COUNTIF($U$10:$U22," - ")&lt;ROUNDDOWN(F28*0.45,0),F28-COUNTIF($U$10:$U22," - "),ROUNDDOWN(F28*0.45,0)))</f>
         <v/>
       </c>
       <c r="G31" s="6" t="n"/>
@@ -7783,7 +7783,7 @@
       <c r="O31" s="6" t="n"/>
       <c r="P31" s="56" t="inlineStr">
         <is>
-          <t>Margarita BRITIKOVA</t>
+          <t>Маргарита БРІТІКОВА</t>
         </is>
       </c>
       <c r="Q31" s="54" t="n"/>
@@ -8099,7 +8099,7 @@
       <c r="B5" s="12" t="n"/>
       <c r="C5" s="73" t="inlineStr">
         <is>
-          <t>Успішності студентів спеціальності G13 ««Харчові технології»»</t>
+          <t>Успішності студентів спеціальності G13 «Харчові технології»</t>
         </is>
       </c>
       <c r="D5" s="92" t="n"/>
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="F19" s="63">
-        <f>IF(F16="Очікую","Очікую",IF(F16-COUNTIF($U$10:$U10," - ")&lt;ROUNDDOWN(F16*0.4,0),F16-COUNTIF($U$10:$U10," - "),ROUNDDOWN(F16*0.4,0)))</f>
+        <f>IF(F16="Очікую","Очікую",IF(F16-COUNTIF($U$10:$U10," - ")&lt;ROUNDDOWN(F16*0.45,0),F16-COUNTIF($U$10:$U10," - "),ROUNDDOWN(F16*0.45,0)))</f>
         <v/>
       </c>
       <c r="G19" s="6" t="n"/>
@@ -8796,7 +8796,7 @@
       <c r="O19" s="6" t="n"/>
       <c r="P19" s="56" t="inlineStr">
         <is>
-          <t>Margarita BRITIKOVA</t>
+          <t>Маргарита БРІТІКОВА</t>
         </is>
       </c>
       <c r="Q19" s="54" t="n"/>
@@ -9124,7 +9124,7 @@
       <c r="B5" s="12" t="n"/>
       <c r="C5" s="73" t="inlineStr">
         <is>
-          <t>Успішності студентів спеціальності J2 ««Готельно-ресторанна справа та кейтеринг»»</t>
+          <t>Успішності студентів спеціальності J2 «Готельно-ресторанна справа та кейтеринг»</t>
         </is>
       </c>
       <c r="D5" s="92" t="n"/>
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="F19" s="63">
-        <f>IF(F16="Очікую","Очікую",IF(F16-COUNTIF($U$10:$U10," - ")&lt;ROUNDDOWN(F16*0.4,0),F16-COUNTIF($U$10:$U10," - "),ROUNDDOWN(F16*0.4,0)))</f>
+        <f>IF(F16="Очікую","Очікую",IF(F16-COUNTIF($U$10:$U10," - ")&lt;ROUNDDOWN(F16*0.45,0),F16-COUNTIF($U$10:$U10," - "),ROUNDDOWN(F16*0.45,0)))</f>
         <v/>
       </c>
       <c r="G19" s="6" t="n"/>
@@ -9821,7 +9821,7 @@
       <c r="O19" s="6" t="n"/>
       <c r="P19" s="56" t="inlineStr">
         <is>
-          <t>Margarita BRITIKOVA</t>
+          <t>Маргарита БРІТІКОВА</t>
         </is>
       </c>
       <c r="Q19" s="54" t="n"/>
@@ -10149,7 +10149,7 @@
       <c r="B5" s="12" t="n"/>
       <c r="C5" s="73" t="inlineStr">
         <is>
-          <t>Успішності студентів спеціальності J3 ««Туризм та рекреація»»</t>
+          <t>Успішності студентів спеціальності J3 «Туризм та рекреація»</t>
         </is>
       </c>
       <c r="D5" s="92" t="n"/>
@@ -10909,7 +10909,7 @@
         </is>
       </c>
       <c r="F20" s="63">
-        <f>IF(F17="Очікую","Очікую",IF(F17-COUNTIF($U$10:$U11," - ")&lt;ROUNDDOWN(F17*0.4,0),F17-COUNTIF($U$10:$U11," - "),ROUNDDOWN(F17*0.4,0)))</f>
+        <f>IF(F17="Очікую","Очікую",IF(F17-COUNTIF($U$10:$U11," - ")&lt;ROUNDDOWN(F17*0.45,0),F17-COUNTIF($U$10:$U11," - "),ROUNDDOWN(F17*0.45,0)))</f>
         <v/>
       </c>
       <c r="G20" s="6" t="n"/>
@@ -10927,7 +10927,7 @@
       <c r="O20" s="6" t="n"/>
       <c r="P20" s="56" t="inlineStr">
         <is>
-          <t>Margarita BRITIKOVA</t>
+          <t>Маргарита БРІТІКОВА</t>
         </is>
       </c>
       <c r="Q20" s="54" t="n"/>
